--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848567</v>
+        <v>124848569</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,46 +1314,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Åsmyrvallen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458147</v>
+        <v>457975</v>
       </c>
       <c r="R8" t="n">
-        <v>6925754</v>
+        <v>6926127</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bohål 4m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848569</v>
+        <v>124848571</v>
       </c>
       <c r="B9" t="n">
         <v>91705</v>
@@ -1457,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457975</v>
+        <v>458353</v>
       </c>
       <c r="R9" t="n">
-        <v>6926127</v>
+        <v>6926238</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848571</v>
+        <v>124848585</v>
       </c>
       <c r="B10" t="n">
-        <v>91705</v>
+        <v>88359</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1559,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458353</v>
+        <v>457899</v>
       </c>
       <c r="R10" t="n">
-        <v>6926238</v>
+        <v>6925794</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1621,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848585</v>
+        <v>124848587</v>
       </c>
       <c r="B11" t="n">
         <v>88359</v>
@@ -1661,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457899</v>
+        <v>458267</v>
       </c>
       <c r="R11" t="n">
-        <v>6925794</v>
+        <v>6926231</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1723,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848587</v>
+        <v>124848581</v>
       </c>
       <c r="B12" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1739,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1763,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458267</v>
+        <v>458158</v>
       </c>
       <c r="R12" t="n">
-        <v>6926231</v>
+        <v>6925727</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,6 +1786,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1825,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848581</v>
+        <v>124848564</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1841,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1865,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458158</v>
+        <v>458403</v>
       </c>
       <c r="R13" t="n">
-        <v>6925727</v>
+        <v>6926243</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1905,7 +1897,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848564</v>
+        <v>124848568</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,25 +1936,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1972,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458403</v>
+        <v>457868</v>
       </c>
       <c r="R14" t="n">
-        <v>6926243</v>
+        <v>6925885</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,11 +2000,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848568</v>
+        <v>124848580</v>
       </c>
       <c r="B15" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,25 +2038,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2079,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457868</v>
+        <v>457954</v>
       </c>
       <c r="R15" t="n">
-        <v>6925885</v>
+        <v>6925697</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2115,6 +2102,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2141,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848580</v>
+        <v>124848566</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2181,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457954</v>
+        <v>458023</v>
       </c>
       <c r="R16" t="n">
-        <v>6925697</v>
+        <v>6926101</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2221,7 +2213,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2248,7 +2240,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848566</v>
+        <v>124848567</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2282,16 +2274,24 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Åsmyrvallen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458023</v>
+        <v>458147</v>
       </c>
       <c r="R17" t="n">
-        <v>6926101</v>
+        <v>6925754</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Bohål 4m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848588</v>
+        <v>124848564</v>
       </c>
       <c r="B2" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458411</v>
+        <v>458403</v>
       </c>
       <c r="R2" t="n">
-        <v>6926214</v>
+        <v>6926243</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848562</v>
+        <v>124848585</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457950</v>
+        <v>457899</v>
       </c>
       <c r="R3" t="n">
-        <v>6925736</v>
+        <v>6925794</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848550</v>
+        <v>124848568</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457870</v>
+        <v>457868</v>
       </c>
       <c r="R4" t="n">
-        <v>6925918</v>
+        <v>6925885</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848582</v>
+        <v>124848580</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458088</v>
+        <v>457954</v>
       </c>
       <c r="R5" t="n">
-        <v>6926145</v>
+        <v>6925697</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848561</v>
+        <v>124848566</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457895</v>
+        <v>458023</v>
       </c>
       <c r="R6" t="n">
-        <v>6925641</v>
+        <v>6926101</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848575</v>
+        <v>124848550</v>
       </c>
       <c r="B7" t="n">
-        <v>78889</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458248</v>
+        <v>457870</v>
       </c>
       <c r="R7" t="n">
-        <v>6926223</v>
+        <v>6925918</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848569</v>
+        <v>124848575</v>
       </c>
       <c r="B8" t="n">
-        <v>91705</v>
+        <v>78889</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1314,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457975</v>
+        <v>458248</v>
       </c>
       <c r="R8" t="n">
-        <v>6926127</v>
+        <v>6926223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848571</v>
+        <v>124848587</v>
       </c>
       <c r="B9" t="n">
-        <v>91705</v>
+        <v>88359</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>67</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458353</v>
+        <v>458267</v>
       </c>
       <c r="R9" t="n">
-        <v>6926238</v>
+        <v>6926231</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848585</v>
+        <v>124848571</v>
       </c>
       <c r="B10" t="n">
-        <v>88359</v>
+        <v>91705</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>67</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457899</v>
+        <v>458353</v>
       </c>
       <c r="R10" t="n">
-        <v>6925794</v>
+        <v>6926238</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848587</v>
+        <v>124848582</v>
       </c>
       <c r="B11" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458267</v>
+        <v>458088</v>
       </c>
       <c r="R11" t="n">
-        <v>6926231</v>
+        <v>6926145</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,6 +1684,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848581</v>
+        <v>124848588</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458158</v>
+        <v>458411</v>
       </c>
       <c r="R12" t="n">
-        <v>6925727</v>
+        <v>6926214</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,11 +1791,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848564</v>
+        <v>124848569</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458403</v>
+        <v>457975</v>
       </c>
       <c r="R13" t="n">
-        <v>6926243</v>
+        <v>6926127</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,11 +1893,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848568</v>
+        <v>124848581</v>
       </c>
       <c r="B14" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,25 +1931,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457868</v>
+        <v>458158</v>
       </c>
       <c r="R14" t="n">
-        <v>6925885</v>
+        <v>6925727</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,6 +1995,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848580</v>
+        <v>124848561</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457954</v>
+        <v>457895</v>
       </c>
       <c r="R15" t="n">
-        <v>6925697</v>
+        <v>6925641</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,7 +2133,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848566</v>
+        <v>124848562</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458023</v>
+        <v>457950</v>
       </c>
       <c r="R16" t="n">
-        <v>6926101</v>
+        <v>6925736</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848587</v>
+        <v>124848582</v>
       </c>
       <c r="B9" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458267</v>
+        <v>458088</v>
       </c>
       <c r="R9" t="n">
-        <v>6926231</v>
+        <v>6926145</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848571</v>
+        <v>124848587</v>
       </c>
       <c r="B10" t="n">
-        <v>91705</v>
+        <v>88359</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1523,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458353</v>
+        <v>458267</v>
       </c>
       <c r="R10" t="n">
-        <v>6926238</v>
+        <v>6926231</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848582</v>
+        <v>124848571</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1625,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458088</v>
+        <v>458353</v>
       </c>
       <c r="R11" t="n">
-        <v>6926145</v>
+        <v>6926238</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848564</v>
+        <v>124848585</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458403</v>
+        <v>457899</v>
       </c>
       <c r="R2" t="n">
-        <v>6926243</v>
+        <v>6925794</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848585</v>
+        <v>124848564</v>
       </c>
       <c r="B3" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457899</v>
+        <v>458403</v>
       </c>
       <c r="R3" t="n">
-        <v>6925794</v>
+        <v>6926243</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848568</v>
+        <v>124848575</v>
       </c>
       <c r="B4" t="n">
-        <v>91705</v>
+        <v>78889</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457868</v>
+        <v>458248</v>
       </c>
       <c r="R4" t="n">
-        <v>6925885</v>
+        <v>6926223</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848566</v>
+        <v>124848582</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458023</v>
+        <v>458088</v>
       </c>
       <c r="R6" t="n">
-        <v>6926101</v>
+        <v>6926145</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848550</v>
+        <v>124848562</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457870</v>
+        <v>457950</v>
       </c>
       <c r="R7" t="n">
-        <v>6925918</v>
+        <v>6925736</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848575</v>
+        <v>124848588</v>
       </c>
       <c r="B8" t="n">
-        <v>78889</v>
+        <v>88359</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458248</v>
+        <v>458411</v>
       </c>
       <c r="R8" t="n">
-        <v>6926223</v>
+        <v>6926214</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848582</v>
+        <v>124848587</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458088</v>
+        <v>458267</v>
       </c>
       <c r="R9" t="n">
-        <v>6926145</v>
+        <v>6926231</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848587</v>
+        <v>124848581</v>
       </c>
       <c r="B10" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458267</v>
+        <v>458158</v>
       </c>
       <c r="R10" t="n">
-        <v>6926231</v>
+        <v>6925727</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,6 +1587,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848571</v>
+        <v>124848550</v>
       </c>
       <c r="B11" t="n">
-        <v>91705</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,25 +1630,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458353</v>
+        <v>457870</v>
       </c>
       <c r="R11" t="n">
-        <v>6926238</v>
+        <v>6925918</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848588</v>
+        <v>124848561</v>
       </c>
       <c r="B12" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458411</v>
+        <v>457895</v>
       </c>
       <c r="R12" t="n">
-        <v>6926214</v>
+        <v>6925641</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,6 +1796,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848569</v>
+        <v>124848566</v>
       </c>
       <c r="B13" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1839,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457975</v>
+        <v>458023</v>
       </c>
       <c r="R13" t="n">
-        <v>6926127</v>
+        <v>6926101</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,6 +1903,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848581</v>
+        <v>124848568</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,25 +1946,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458158</v>
+        <v>457868</v>
       </c>
       <c r="R14" t="n">
-        <v>6925727</v>
+        <v>6925885</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848561</v>
+        <v>124848569</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,25 +2048,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457895</v>
+        <v>457975</v>
       </c>
       <c r="R15" t="n">
-        <v>6925641</v>
+        <v>6926127</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,11 +2112,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848562</v>
+        <v>124848571</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,25 +2150,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457950</v>
+        <v>458353</v>
       </c>
       <c r="R16" t="n">
-        <v>6925736</v>
+        <v>6926238</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,11 +2214,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848585</v>
+        <v>124848562</v>
       </c>
       <c r="B2" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457899</v>
+        <v>457950</v>
       </c>
       <c r="R2" t="n">
-        <v>6925794</v>
+        <v>6925736</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848564</v>
+        <v>124848587</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458403</v>
+        <v>458267</v>
       </c>
       <c r="R3" t="n">
-        <v>6926243</v>
+        <v>6926231</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848575</v>
+        <v>124848561</v>
       </c>
       <c r="B4" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458248</v>
+        <v>457895</v>
       </c>
       <c r="R4" t="n">
-        <v>6926223</v>
+        <v>6925641</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848580</v>
+        <v>124848569</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457954</v>
+        <v>457975</v>
       </c>
       <c r="R5" t="n">
-        <v>6925697</v>
+        <v>6926127</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848582</v>
+        <v>124848575</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458088</v>
+        <v>458248</v>
       </c>
       <c r="R6" t="n">
-        <v>6926145</v>
+        <v>6926223</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848562</v>
+        <v>124848568</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457950</v>
+        <v>457868</v>
       </c>
       <c r="R7" t="n">
-        <v>6925736</v>
+        <v>6925885</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848588</v>
+        <v>124848571</v>
       </c>
       <c r="B8" t="n">
-        <v>88359</v>
+        <v>91705</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>67</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458411</v>
+        <v>458353</v>
       </c>
       <c r="R8" t="n">
-        <v>6926214</v>
+        <v>6926238</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848587</v>
+        <v>124848564</v>
       </c>
       <c r="B9" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458267</v>
+        <v>458403</v>
       </c>
       <c r="R9" t="n">
-        <v>6926231</v>
+        <v>6926243</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848581</v>
+        <v>124848566</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458158</v>
+        <v>458023</v>
       </c>
       <c r="R10" t="n">
-        <v>6925727</v>
+        <v>6926101</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1591,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848550</v>
+        <v>124848580</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457870</v>
+        <v>457954</v>
       </c>
       <c r="R11" t="n">
-        <v>6925918</v>
+        <v>6925697</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1689,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848561</v>
+        <v>124848585</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457895</v>
+        <v>457899</v>
       </c>
       <c r="R12" t="n">
-        <v>6925641</v>
+        <v>6925794</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848566</v>
+        <v>124848588</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458023</v>
+        <v>458411</v>
       </c>
       <c r="R13" t="n">
-        <v>6926101</v>
+        <v>6926214</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848568</v>
+        <v>124848581</v>
       </c>
       <c r="B14" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1946,25 +1936,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457868</v>
+        <v>458158</v>
       </c>
       <c r="R14" t="n">
-        <v>6925885</v>
+        <v>6925727</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,6 +2000,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848569</v>
+        <v>124848582</v>
       </c>
       <c r="B15" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2048,25 +2043,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457975</v>
+        <v>458088</v>
       </c>
       <c r="R15" t="n">
-        <v>6926127</v>
+        <v>6926145</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,6 +2107,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848571</v>
+        <v>124848550</v>
       </c>
       <c r="B16" t="n">
-        <v>91705</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2150,25 +2150,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458353</v>
+        <v>457870</v>
       </c>
       <c r="R16" t="n">
-        <v>6926238</v>
+        <v>6925918</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848568</v>
+        <v>124848571</v>
       </c>
       <c r="B7" t="n">
         <v>91705</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457868</v>
+        <v>458353</v>
       </c>
       <c r="R7" t="n">
-        <v>6925885</v>
+        <v>6926238</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848571</v>
+        <v>124848568</v>
       </c>
       <c r="B8" t="n">
         <v>91705</v>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458353</v>
+        <v>457868</v>
       </c>
       <c r="R8" t="n">
-        <v>6926238</v>
+        <v>6925885</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848562</v>
+        <v>124848575</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457950</v>
+        <v>458248</v>
       </c>
       <c r="R2" t="n">
-        <v>6925736</v>
+        <v>6926223</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848587</v>
+        <v>124848566</v>
       </c>
       <c r="B3" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458267</v>
+        <v>458023</v>
       </c>
       <c r="R3" t="n">
-        <v>6926231</v>
+        <v>6926101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848561</v>
+        <v>124848562</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457895</v>
+        <v>457950</v>
       </c>
       <c r="R4" t="n">
-        <v>6925641</v>
+        <v>6925736</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848569</v>
+        <v>124848588</v>
       </c>
       <c r="B5" t="n">
-        <v>91705</v>
+        <v>88359</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457975</v>
+        <v>458411</v>
       </c>
       <c r="R5" t="n">
-        <v>6926127</v>
+        <v>6926214</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848575</v>
+        <v>124848561</v>
       </c>
       <c r="B6" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458248</v>
+        <v>457895</v>
       </c>
       <c r="R6" t="n">
-        <v>6926223</v>
+        <v>6925641</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848571</v>
+        <v>124848550</v>
       </c>
       <c r="B7" t="n">
-        <v>91705</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458353</v>
+        <v>457870</v>
       </c>
       <c r="R7" t="n">
-        <v>6926238</v>
+        <v>6925918</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848568</v>
+        <v>124848569</v>
       </c>
       <c r="B8" t="n">
         <v>91705</v>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457868</v>
+        <v>457975</v>
       </c>
       <c r="R8" t="n">
-        <v>6925885</v>
+        <v>6926127</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848564</v>
+        <v>124848585</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458403</v>
+        <v>457899</v>
       </c>
       <c r="R9" t="n">
-        <v>6926243</v>
+        <v>6925794</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848566</v>
+        <v>124848581</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458023</v>
+        <v>458158</v>
       </c>
       <c r="R10" t="n">
-        <v>6926101</v>
+        <v>6925727</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848580</v>
+        <v>124848564</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457954</v>
+        <v>458403</v>
       </c>
       <c r="R11" t="n">
-        <v>6925697</v>
+        <v>6926243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,7 +1720,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848585</v>
+        <v>124848587</v>
       </c>
       <c r="B12" t="n">
         <v>88359</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457899</v>
+        <v>458267</v>
       </c>
       <c r="R12" t="n">
-        <v>6925794</v>
+        <v>6926231</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848588</v>
+        <v>124848568</v>
       </c>
       <c r="B13" t="n">
-        <v>88359</v>
+        <v>91705</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>67</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458411</v>
+        <v>457868</v>
       </c>
       <c r="R13" t="n">
-        <v>6926214</v>
+        <v>6925885</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848581</v>
+        <v>124848571</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,25 +1936,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458158</v>
+        <v>458353</v>
       </c>
       <c r="R14" t="n">
-        <v>6925727</v>
+        <v>6926238</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,11 +2000,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848550</v>
+        <v>124848580</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457870</v>
+        <v>457954</v>
       </c>
       <c r="R16" t="n">
-        <v>6925918</v>
+        <v>6925697</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,6 +2209,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848564</v>
+        <v>124848587</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458403</v>
+        <v>458267</v>
       </c>
       <c r="R11" t="n">
-        <v>6926243</v>
+        <v>6926231</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848587</v>
+        <v>124848568</v>
       </c>
       <c r="B12" t="n">
-        <v>88359</v>
+        <v>91705</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>67</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458267</v>
+        <v>457868</v>
       </c>
       <c r="R12" t="n">
-        <v>6926231</v>
+        <v>6925885</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848568</v>
+        <v>124848564</v>
       </c>
       <c r="B13" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457868</v>
+        <v>458403</v>
       </c>
       <c r="R13" t="n">
-        <v>6925885</v>
+        <v>6926243</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,6 +1893,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848575</v>
+        <v>124848550</v>
       </c>
       <c r="B2" t="n">
-        <v>78889</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458248</v>
+        <v>457870</v>
       </c>
       <c r="R2" t="n">
-        <v>6926223</v>
+        <v>6925918</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848566</v>
+        <v>124848575</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458023</v>
+        <v>458248</v>
       </c>
       <c r="R3" t="n">
-        <v>6926101</v>
+        <v>6926223</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848562</v>
+        <v>124848582</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457950</v>
+        <v>458088</v>
       </c>
       <c r="R4" t="n">
-        <v>6925736</v>
+        <v>6926145</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848588</v>
+        <v>124848580</v>
       </c>
       <c r="B5" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458411</v>
+        <v>457954</v>
       </c>
       <c r="R5" t="n">
-        <v>6926214</v>
+        <v>6925697</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848561</v>
+        <v>124848588</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457895</v>
+        <v>458411</v>
       </c>
       <c r="R6" t="n">
-        <v>6925641</v>
+        <v>6926214</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848550</v>
+        <v>124848587</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457870</v>
+        <v>458267</v>
       </c>
       <c r="R7" t="n">
-        <v>6925918</v>
+        <v>6926231</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848569</v>
+        <v>124848568</v>
       </c>
       <c r="B8" t="n">
         <v>91705</v>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457975</v>
+        <v>457868</v>
       </c>
       <c r="R8" t="n">
-        <v>6926127</v>
+        <v>6925885</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848585</v>
+        <v>124848566</v>
       </c>
       <c r="B9" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457899</v>
+        <v>458023</v>
       </c>
       <c r="R9" t="n">
-        <v>6925794</v>
+        <v>6926101</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848581</v>
+        <v>124848569</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458158</v>
+        <v>457975</v>
       </c>
       <c r="R10" t="n">
-        <v>6925727</v>
+        <v>6926127</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,11 +1582,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848587</v>
+        <v>124848581</v>
       </c>
       <c r="B11" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458267</v>
+        <v>458158</v>
       </c>
       <c r="R11" t="n">
-        <v>6926231</v>
+        <v>6925727</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,6 +1684,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848568</v>
+        <v>124848561</v>
       </c>
       <c r="B12" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457868</v>
+        <v>457895</v>
       </c>
       <c r="R12" t="n">
-        <v>6925885</v>
+        <v>6925641</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848564</v>
+        <v>124848562</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1857,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458403</v>
+        <v>457950</v>
       </c>
       <c r="R13" t="n">
-        <v>6926243</v>
+        <v>6925736</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848571</v>
+        <v>124848564</v>
       </c>
       <c r="B14" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,25 +1941,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458353</v>
+        <v>458403</v>
       </c>
       <c r="R14" t="n">
-        <v>6926238</v>
+        <v>6926243</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,6 +2005,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848582</v>
+        <v>124848571</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,25 +2048,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458088</v>
+        <v>458353</v>
       </c>
       <c r="R15" t="n">
-        <v>6926145</v>
+        <v>6926238</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,11 +2112,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848580</v>
+        <v>124848585</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,21 +2154,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457954</v>
+        <v>457899</v>
       </c>
       <c r="R16" t="n">
-        <v>6925697</v>
+        <v>6925794</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,11 +2214,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848550</v>
+        <v>124848569</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457870</v>
+        <v>457975</v>
       </c>
       <c r="R2" t="n">
-        <v>6925918</v>
+        <v>6926127</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848575</v>
+        <v>124848550</v>
       </c>
       <c r="B3" t="n">
-        <v>78889</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458248</v>
+        <v>457870</v>
       </c>
       <c r="R3" t="n">
-        <v>6926223</v>
+        <v>6925918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848582</v>
+        <v>124848566</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458088</v>
+        <v>458023</v>
       </c>
       <c r="R4" t="n">
-        <v>6926145</v>
+        <v>6926101</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848580</v>
+        <v>124848581</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457954</v>
+        <v>458158</v>
       </c>
       <c r="R5" t="n">
-        <v>6925697</v>
+        <v>6925727</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848587</v>
+        <v>124848585</v>
       </c>
       <c r="B7" t="n">
         <v>88359</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458267</v>
+        <v>457899</v>
       </c>
       <c r="R7" t="n">
-        <v>6926231</v>
+        <v>6925794</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848568</v>
+        <v>124848582</v>
       </c>
       <c r="B8" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457868</v>
+        <v>458088</v>
       </c>
       <c r="R8" t="n">
-        <v>6925885</v>
+        <v>6926145</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848566</v>
+        <v>124848587</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458023</v>
+        <v>458267</v>
       </c>
       <c r="R9" t="n">
-        <v>6926101</v>
+        <v>6926231</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848569</v>
+        <v>124848568</v>
       </c>
       <c r="B10" t="n">
         <v>91705</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457975</v>
+        <v>457868</v>
       </c>
       <c r="R10" t="n">
-        <v>6926127</v>
+        <v>6925885</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848581</v>
+        <v>124848562</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458158</v>
+        <v>457950</v>
       </c>
       <c r="R11" t="n">
-        <v>6925727</v>
+        <v>6925736</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848561</v>
+        <v>124848564</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457895</v>
+        <v>458403</v>
       </c>
       <c r="R12" t="n">
-        <v>6925641</v>
+        <v>6926243</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848562</v>
+        <v>124848561</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457950</v>
+        <v>457895</v>
       </c>
       <c r="R13" t="n">
-        <v>6925736</v>
+        <v>6925641</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848564</v>
+        <v>124848575</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458403</v>
+        <v>458248</v>
       </c>
       <c r="R14" t="n">
-        <v>6926243</v>
+        <v>6926223</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,11 +2005,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848585</v>
+        <v>124848580</v>
       </c>
       <c r="B16" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457899</v>
+        <v>457954</v>
       </c>
       <c r="R16" t="n">
-        <v>6925794</v>
+        <v>6925697</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,6 +2209,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848569</v>
+        <v>124848550</v>
       </c>
       <c r="B2" t="n">
-        <v>91705</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457975</v>
+        <v>457870</v>
       </c>
       <c r="R2" t="n">
-        <v>6926127</v>
+        <v>6925918</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848550</v>
+        <v>124848566</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457870</v>
+        <v>458023</v>
       </c>
       <c r="R3" t="n">
-        <v>6925918</v>
+        <v>6926101</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848566</v>
+        <v>124848587</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458023</v>
+        <v>458267</v>
       </c>
       <c r="R4" t="n">
-        <v>6926101</v>
+        <v>6926231</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848581</v>
+        <v>124848571</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458158</v>
+        <v>458353</v>
       </c>
       <c r="R5" t="n">
-        <v>6925727</v>
+        <v>6926238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848588</v>
+        <v>124848569</v>
       </c>
       <c r="B6" t="n">
-        <v>88359</v>
+        <v>91705</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>67</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458411</v>
+        <v>457975</v>
       </c>
       <c r="R6" t="n">
-        <v>6926214</v>
+        <v>6926127</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848585</v>
+        <v>124848588</v>
       </c>
       <c r="B7" t="n">
         <v>88359</v>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457899</v>
+        <v>458411</v>
       </c>
       <c r="R7" t="n">
-        <v>6925794</v>
+        <v>6926214</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848582</v>
+        <v>124848581</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458088</v>
+        <v>458158</v>
       </c>
       <c r="R8" t="n">
-        <v>6926145</v>
+        <v>6925727</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848587</v>
+        <v>124848585</v>
       </c>
       <c r="B9" t="n">
         <v>88359</v>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458267</v>
+        <v>457899</v>
       </c>
       <c r="R9" t="n">
-        <v>6926231</v>
+        <v>6925794</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848568</v>
+        <v>124848582</v>
       </c>
       <c r="B10" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457868</v>
+        <v>458088</v>
       </c>
       <c r="R10" t="n">
-        <v>6925885</v>
+        <v>6926145</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,6 +1577,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848562</v>
+        <v>124848564</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457950</v>
+        <v>458403</v>
       </c>
       <c r="R11" t="n">
-        <v>6925736</v>
+        <v>6926243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848564</v>
+        <v>124848562</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458403</v>
+        <v>457950</v>
       </c>
       <c r="R12" t="n">
-        <v>6926243</v>
+        <v>6925736</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848561</v>
+        <v>124848568</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457895</v>
+        <v>457868</v>
       </c>
       <c r="R13" t="n">
-        <v>6925641</v>
+        <v>6925885</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848571</v>
+        <v>124848580</v>
       </c>
       <c r="B15" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,25 +2038,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458353</v>
+        <v>457954</v>
       </c>
       <c r="R15" t="n">
-        <v>6926238</v>
+        <v>6925697</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,6 +2102,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848580</v>
+        <v>124848561</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457954</v>
+        <v>457895</v>
       </c>
       <c r="R16" t="n">
-        <v>6925697</v>
+        <v>6925641</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848550</v>
+        <v>124848566</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457870</v>
+        <v>458023</v>
       </c>
       <c r="R2" t="n">
-        <v>6925918</v>
+        <v>6926101</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848566</v>
+        <v>124848569</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458023</v>
+        <v>457975</v>
       </c>
       <c r="R3" t="n">
-        <v>6926101</v>
+        <v>6926127</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848587</v>
+        <v>124848568</v>
       </c>
       <c r="B4" t="n">
-        <v>88359</v>
+        <v>91705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>67</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458267</v>
+        <v>457868</v>
       </c>
       <c r="R4" t="n">
-        <v>6926231</v>
+        <v>6925885</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848571</v>
+        <v>124848575</v>
       </c>
       <c r="B5" t="n">
-        <v>91705</v>
+        <v>78889</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458353</v>
+        <v>458248</v>
       </c>
       <c r="R5" t="n">
-        <v>6926238</v>
+        <v>6926223</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848569</v>
+        <v>124848562</v>
       </c>
       <c r="B6" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457975</v>
+        <v>457950</v>
       </c>
       <c r="R6" t="n">
-        <v>6926127</v>
+        <v>6925736</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848588</v>
+        <v>124848550</v>
       </c>
       <c r="B7" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458411</v>
+        <v>457870</v>
       </c>
       <c r="R7" t="n">
-        <v>6926214</v>
+        <v>6925918</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848581</v>
+        <v>124848580</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458158</v>
+        <v>457954</v>
       </c>
       <c r="R8" t="n">
-        <v>6925727</v>
+        <v>6925697</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848585</v>
+        <v>124848587</v>
       </c>
       <c r="B9" t="n">
         <v>88359</v>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457899</v>
+        <v>458267</v>
       </c>
       <c r="R9" t="n">
-        <v>6925794</v>
+        <v>6926231</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848582</v>
+        <v>124848561</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458088</v>
+        <v>457895</v>
       </c>
       <c r="R10" t="n">
-        <v>6926145</v>
+        <v>6925641</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,7 +1586,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848562</v>
+        <v>124848585</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457950</v>
+        <v>457899</v>
       </c>
       <c r="R12" t="n">
-        <v>6925736</v>
+        <v>6925794</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848568</v>
+        <v>124848581</v>
       </c>
       <c r="B13" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457868</v>
+        <v>458158</v>
       </c>
       <c r="R13" t="n">
-        <v>6925885</v>
+        <v>6925727</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,6 +1898,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848575</v>
+        <v>124848582</v>
       </c>
       <c r="B14" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458248</v>
+        <v>458088</v>
       </c>
       <c r="R14" t="n">
-        <v>6926223</v>
+        <v>6926145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,6 +2005,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848580</v>
+        <v>124848588</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457954</v>
+        <v>458411</v>
       </c>
       <c r="R15" t="n">
-        <v>6925697</v>
+        <v>6926214</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,11 +2112,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848561</v>
+        <v>124848571</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,25 +2150,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457895</v>
+        <v>458353</v>
       </c>
       <c r="R16" t="n">
-        <v>6925641</v>
+        <v>6926238</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,11 +2214,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848569</v>
+        <v>124848581</v>
       </c>
       <c r="B3" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457975</v>
+        <v>458158</v>
       </c>
       <c r="R3" t="n">
-        <v>6926127</v>
+        <v>6925727</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848568</v>
+        <v>124848582</v>
       </c>
       <c r="B4" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457868</v>
+        <v>458088</v>
       </c>
       <c r="R4" t="n">
-        <v>6925885</v>
+        <v>6926145</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1088,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848562</v>
+        <v>124848580</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457950</v>
+        <v>457954</v>
       </c>
       <c r="R6" t="n">
-        <v>6925736</v>
+        <v>6925697</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848550</v>
+        <v>124848564</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457870</v>
+        <v>458403</v>
       </c>
       <c r="R7" t="n">
-        <v>6925918</v>
+        <v>6926243</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1281,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848580</v>
+        <v>124848569</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1324,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457954</v>
+        <v>457975</v>
       </c>
       <c r="R8" t="n">
-        <v>6925697</v>
+        <v>6926127</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848561</v>
+        <v>124848588</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457895</v>
+        <v>458411</v>
       </c>
       <c r="R10" t="n">
-        <v>6925641</v>
+        <v>6926214</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848564</v>
+        <v>124848562</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1653,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458403</v>
+        <v>457950</v>
       </c>
       <c r="R11" t="n">
-        <v>6926243</v>
+        <v>6925736</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848585</v>
+        <v>124848561</v>
       </c>
       <c r="B12" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457899</v>
+        <v>457895</v>
       </c>
       <c r="R12" t="n">
-        <v>6925794</v>
+        <v>6925641</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1801,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848581</v>
+        <v>124848571</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1844,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458158</v>
+        <v>458353</v>
       </c>
       <c r="R13" t="n">
-        <v>6925727</v>
+        <v>6926238</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,11 +1908,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848582</v>
+        <v>124848550</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458088</v>
+        <v>457870</v>
       </c>
       <c r="R14" t="n">
-        <v>6926145</v>
+        <v>6925918</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,7 +2036,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848588</v>
+        <v>124848585</v>
       </c>
       <c r="B15" t="n">
         <v>88359</v>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458411</v>
+        <v>457899</v>
       </c>
       <c r="R15" t="n">
-        <v>6926214</v>
+        <v>6925794</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848571</v>
+        <v>124848568</v>
       </c>
       <c r="B16" t="n">
         <v>91705</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458353</v>
+        <v>457868</v>
       </c>
       <c r="R16" t="n">
-        <v>6926238</v>
+        <v>6925885</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848582</v>
+        <v>124848575</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78889</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458088</v>
+        <v>458248</v>
       </c>
       <c r="R4" t="n">
-        <v>6926145</v>
+        <v>6926223</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848575</v>
+        <v>124848582</v>
       </c>
       <c r="B5" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458248</v>
+        <v>458088</v>
       </c>
       <c r="R5" t="n">
-        <v>6926223</v>
+        <v>6926145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848571</v>
+        <v>124848550</v>
       </c>
       <c r="B13" t="n">
-        <v>91705</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,25 +1844,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458353</v>
+        <v>457870</v>
       </c>
       <c r="R13" t="n">
-        <v>6926238</v>
+        <v>6925918</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848550</v>
+        <v>124848571</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>91705</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1946,25 +1946,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457870</v>
+        <v>458353</v>
       </c>
       <c r="R14" t="n">
-        <v>6925918</v>
+        <v>6926238</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848566</v>
+        <v>124848587</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458023</v>
+        <v>458267</v>
       </c>
       <c r="R2" t="n">
-        <v>6926101</v>
+        <v>6926231</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848581</v>
+        <v>124848564</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458158</v>
+        <v>458403</v>
       </c>
       <c r="R3" t="n">
-        <v>6925727</v>
+        <v>6926243</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848575</v>
+        <v>124848568</v>
       </c>
       <c r="B4" t="n">
-        <v>78889</v>
+        <v>91705</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>67</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458248</v>
+        <v>457868</v>
       </c>
       <c r="R4" t="n">
-        <v>6926223</v>
+        <v>6925885</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848582</v>
+        <v>124848569</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458088</v>
+        <v>457975</v>
       </c>
       <c r="R5" t="n">
-        <v>6926145</v>
+        <v>6926127</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848580</v>
+        <v>124848566</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457954</v>
+        <v>458023</v>
       </c>
       <c r="R6" t="n">
-        <v>6925697</v>
+        <v>6926101</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1168,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848564</v>
+        <v>124848550</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458403</v>
+        <v>457870</v>
       </c>
       <c r="R7" t="n">
-        <v>6926243</v>
+        <v>6925918</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,11 +1271,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848569</v>
+        <v>124848585</v>
       </c>
       <c r="B8" t="n">
-        <v>91705</v>
+        <v>88359</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457975</v>
+        <v>457899</v>
       </c>
       <c r="R8" t="n">
-        <v>6926127</v>
+        <v>6925794</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848587</v>
+        <v>124848588</v>
       </c>
       <c r="B9" t="n">
         <v>88359</v>
@@ -1454,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458267</v>
+        <v>458411</v>
       </c>
       <c r="R9" t="n">
-        <v>6926231</v>
+        <v>6926214</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1516,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848588</v>
+        <v>124848562</v>
       </c>
       <c r="B10" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458411</v>
+        <v>457950</v>
       </c>
       <c r="R10" t="n">
-        <v>6926214</v>
+        <v>6925736</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1577,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848562</v>
+        <v>124848561</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1658,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457950</v>
+        <v>457895</v>
       </c>
       <c r="R11" t="n">
-        <v>6925736</v>
+        <v>6925641</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848561</v>
+        <v>124848581</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457895</v>
+        <v>458158</v>
       </c>
       <c r="R12" t="n">
-        <v>6925641</v>
+        <v>6925727</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1795,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848550</v>
+        <v>124848571</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>91705</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457870</v>
+        <v>458353</v>
       </c>
       <c r="R13" t="n">
-        <v>6925918</v>
+        <v>6926238</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1934,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848571</v>
+        <v>124848575</v>
       </c>
       <c r="B14" t="n">
-        <v>91705</v>
+        <v>78889</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1946,25 +1936,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>67</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458353</v>
+        <v>458248</v>
       </c>
       <c r="R14" t="n">
-        <v>6926238</v>
+        <v>6926223</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848585</v>
+        <v>124848580</v>
       </c>
       <c r="B15" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457899</v>
+        <v>457954</v>
       </c>
       <c r="R15" t="n">
-        <v>6925794</v>
+        <v>6925697</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,6 +2102,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848568</v>
+        <v>124848582</v>
       </c>
       <c r="B16" t="n">
-        <v>91705</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2150,25 +2145,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457868</v>
+        <v>458088</v>
       </c>
       <c r="R16" t="n">
-        <v>6925885</v>
+        <v>6926145</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,6 +2209,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848561</v>
+        <v>124848581</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457895</v>
+        <v>458158</v>
       </c>
       <c r="R11" t="n">
-        <v>6925641</v>
+        <v>6925727</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848581</v>
+        <v>124848561</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458158</v>
+        <v>457895</v>
       </c>
       <c r="R12" t="n">
-        <v>6925727</v>
+        <v>6925641</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848587</v>
+        <v>124848580</v>
       </c>
       <c r="B2" t="n">
-        <v>88359</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>458267</v>
+        <v>457954</v>
       </c>
       <c r="R2" t="n">
-        <v>6926231</v>
+        <v>6925697</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848564</v>
+        <v>124848585</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458403</v>
+        <v>457899</v>
       </c>
       <c r="R3" t="n">
-        <v>6926243</v>
+        <v>6925794</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848568</v>
+        <v>124848550</v>
       </c>
       <c r="B4" t="n">
-        <v>91705</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457868</v>
+        <v>457870</v>
       </c>
       <c r="R4" t="n">
-        <v>6925885</v>
+        <v>6925918</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848569</v>
+        <v>124848568</v>
       </c>
       <c r="B5" t="n">
         <v>91705</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457975</v>
+        <v>457868</v>
       </c>
       <c r="R5" t="n">
-        <v>6926127</v>
+        <v>6925885</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848566</v>
+        <v>124848562</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>458023</v>
+        <v>457950</v>
       </c>
       <c r="R6" t="n">
-        <v>6926101</v>
+        <v>6925736</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848550</v>
+        <v>124848581</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457870</v>
+        <v>458158</v>
       </c>
       <c r="R7" t="n">
-        <v>6925918</v>
+        <v>6925727</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848585</v>
+        <v>124848571</v>
       </c>
       <c r="B8" t="n">
-        <v>88359</v>
+        <v>91705</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1314,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>67</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457899</v>
+        <v>458353</v>
       </c>
       <c r="R8" t="n">
-        <v>6925794</v>
+        <v>6926238</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848588</v>
+        <v>124848575</v>
       </c>
       <c r="B9" t="n">
-        <v>88359</v>
+        <v>78889</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>864</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458411</v>
+        <v>458248</v>
       </c>
       <c r="R9" t="n">
-        <v>6926214</v>
+        <v>6926223</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848562</v>
+        <v>124848566</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457950</v>
+        <v>458023</v>
       </c>
       <c r="R10" t="n">
-        <v>6925736</v>
+        <v>6926101</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848581</v>
+        <v>124848561</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458158</v>
+        <v>457895</v>
       </c>
       <c r="R11" t="n">
-        <v>6925727</v>
+        <v>6925641</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,7 +1693,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848561</v>
+        <v>124848587</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457895</v>
+        <v>458267</v>
       </c>
       <c r="R12" t="n">
-        <v>6925641</v>
+        <v>6926231</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848571</v>
+        <v>124848564</v>
       </c>
       <c r="B13" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458353</v>
+        <v>458403</v>
       </c>
       <c r="R13" t="n">
-        <v>6926238</v>
+        <v>6926243</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,6 +1898,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848575</v>
+        <v>124848582</v>
       </c>
       <c r="B14" t="n">
-        <v>78889</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458248</v>
+        <v>458088</v>
       </c>
       <c r="R14" t="n">
-        <v>6926223</v>
+        <v>6926145</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,6 +2005,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848580</v>
+        <v>124848569</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>91705</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,25 +2048,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457954</v>
+        <v>457975</v>
       </c>
       <c r="R15" t="n">
-        <v>6925697</v>
+        <v>6926127</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,11 +2112,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848582</v>
+        <v>124848588</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,21 +2154,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458088</v>
+        <v>458411</v>
       </c>
       <c r="R16" t="n">
-        <v>6926145</v>
+        <v>6926214</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,11 +2214,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848580</v>
+        <v>124848561</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457954</v>
+        <v>457895</v>
       </c>
       <c r="R2" t="n">
-        <v>6925697</v>
+        <v>6925641</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848585</v>
+        <v>124848564</v>
       </c>
       <c r="B3" t="n">
-        <v>88359</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457899</v>
+        <v>458403</v>
       </c>
       <c r="R3" t="n">
-        <v>6925794</v>
+        <v>6926243</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848550</v>
+        <v>124848581</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457870</v>
+        <v>458158</v>
       </c>
       <c r="R4" t="n">
-        <v>6925918</v>
+        <v>6925727</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +965,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848568</v>
+        <v>124848582</v>
       </c>
       <c r="B5" t="n">
-        <v>91705</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457868</v>
+        <v>458088</v>
       </c>
       <c r="R5" t="n">
-        <v>6925885</v>
+        <v>6926145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848562</v>
+        <v>124848568</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91865</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1115,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457950</v>
+        <v>457868</v>
       </c>
       <c r="R6" t="n">
-        <v>6925736</v>
+        <v>6925885</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848581</v>
+        <v>124848575</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>79026</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458158</v>
+        <v>458248</v>
       </c>
       <c r="R7" t="n">
-        <v>6925727</v>
+        <v>6926223</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848571</v>
+        <v>124848566</v>
       </c>
       <c r="B8" t="n">
-        <v>91705</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458353</v>
+        <v>458023</v>
       </c>
       <c r="R8" t="n">
-        <v>6926238</v>
+        <v>6926101</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848575</v>
+        <v>124848580</v>
       </c>
       <c r="B9" t="n">
-        <v>78889</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>458248</v>
+        <v>457954</v>
       </c>
       <c r="R9" t="n">
-        <v>6926223</v>
+        <v>6925697</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848566</v>
+        <v>124848562</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1546,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>458023</v>
+        <v>457950</v>
       </c>
       <c r="R10" t="n">
-        <v>6926101</v>
+        <v>6925736</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848561</v>
+        <v>124848585</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>88512</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457895</v>
+        <v>457899</v>
       </c>
       <c r="R11" t="n">
-        <v>6925641</v>
+        <v>6925794</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,11 +1704,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848587</v>
+        <v>124848569</v>
       </c>
       <c r="B12" t="n">
-        <v>88359</v>
+        <v>91865</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,25 +1742,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>67</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458267</v>
+        <v>457975</v>
       </c>
       <c r="R12" t="n">
-        <v>6926231</v>
+        <v>6926127</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848564</v>
+        <v>124848588</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>88512</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458403</v>
+        <v>458411</v>
       </c>
       <c r="R13" t="n">
-        <v>6926243</v>
+        <v>6926214</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,11 +1908,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1929,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848582</v>
+        <v>124848550</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>458088</v>
+        <v>457870</v>
       </c>
       <c r="R14" t="n">
-        <v>6926145</v>
+        <v>6925918</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848569</v>
+        <v>124848587</v>
       </c>
       <c r="B15" t="n">
-        <v>91705</v>
+        <v>88512</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2048,25 +2048,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>67</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457975</v>
+        <v>458267</v>
       </c>
       <c r="R15" t="n">
-        <v>6926127</v>
+        <v>6926231</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848588</v>
+        <v>124848571</v>
       </c>
       <c r="B16" t="n">
-        <v>88359</v>
+        <v>91865</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2150,25 +2150,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>67</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458411</v>
+        <v>458353</v>
       </c>
       <c r="R16" t="n">
-        <v>6926214</v>
+        <v>6926238</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
         <v>124848567</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -1730,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848569</v>
+        <v>124848588</v>
       </c>
       <c r="B12" t="n">
-        <v>91865</v>
+        <v>88512</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1742,25 +1742,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457975</v>
+        <v>458411</v>
       </c>
       <c r="R12" t="n">
-        <v>6926127</v>
+        <v>6926214</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848588</v>
+        <v>124848569</v>
       </c>
       <c r="B13" t="n">
-        <v>88512</v>
+        <v>91865</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,25 +1844,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>67</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>458411</v>
+        <v>457975</v>
       </c>
       <c r="R13" t="n">
-        <v>6926214</v>
+        <v>6926127</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848561</v>
+        <v>124848575</v>
       </c>
       <c r="B2" t="n">
-        <v>57635</v>
+        <v>79026</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457895</v>
+        <v>458248</v>
       </c>
       <c r="R2" t="n">
-        <v>6925641</v>
+        <v>6926223</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848564</v>
+        <v>124848587</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>88512</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>458403</v>
+        <v>458267</v>
       </c>
       <c r="R3" t="n">
-        <v>6926243</v>
+        <v>6926231</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848581</v>
+        <v>124848564</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>458158</v>
+        <v>458403</v>
       </c>
       <c r="R4" t="n">
-        <v>6925727</v>
+        <v>6926243</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848582</v>
+        <v>124848571</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>91865</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458088</v>
+        <v>458353</v>
       </c>
       <c r="R5" t="n">
-        <v>6926145</v>
+        <v>6926238</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848568</v>
+        <v>124848582</v>
       </c>
       <c r="B6" t="n">
-        <v>91865</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457868</v>
+        <v>458088</v>
       </c>
       <c r="R6" t="n">
-        <v>6925885</v>
+        <v>6926145</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848575</v>
+        <v>124848581</v>
       </c>
       <c r="B7" t="n">
-        <v>79026</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>458248</v>
+        <v>458158</v>
       </c>
       <c r="R7" t="n">
-        <v>6926223</v>
+        <v>6925727</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848566</v>
+        <v>124848588</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
+        <v>88512</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>458023</v>
+        <v>458411</v>
       </c>
       <c r="R8" t="n">
-        <v>6926101</v>
+        <v>6926214</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848580</v>
+        <v>124848550</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457954</v>
+        <v>457870</v>
       </c>
       <c r="R9" t="n">
-        <v>6925697</v>
+        <v>6925918</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848562</v>
+        <v>124848569</v>
       </c>
       <c r="B10" t="n">
-        <v>57635</v>
+        <v>91865</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1533,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457950</v>
+        <v>457975</v>
       </c>
       <c r="R10" t="n">
-        <v>6925736</v>
+        <v>6926127</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1582,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848588</v>
+        <v>124848562</v>
       </c>
       <c r="B12" t="n">
-        <v>88512</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458411</v>
+        <v>457950</v>
       </c>
       <c r="R12" t="n">
-        <v>6926214</v>
+        <v>6925736</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,6 +1786,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848569</v>
+        <v>124848566</v>
       </c>
       <c r="B13" t="n">
-        <v>91865</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457975</v>
+        <v>458023</v>
       </c>
       <c r="R13" t="n">
-        <v>6926127</v>
+        <v>6926101</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,6 +1893,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848550</v>
+        <v>124848561</v>
       </c>
       <c r="B14" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457870</v>
+        <v>457895</v>
       </c>
       <c r="R14" t="n">
-        <v>6925918</v>
+        <v>6925641</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,6 +2000,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848587</v>
+        <v>124848580</v>
       </c>
       <c r="B15" t="n">
-        <v>88512</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,21 +2047,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458267</v>
+        <v>457954</v>
       </c>
       <c r="R15" t="n">
-        <v>6926231</v>
+        <v>6925697</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,6 +2107,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,7 +2138,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848571</v>
+        <v>124848568</v>
       </c>
       <c r="B16" t="n">
         <v>91865</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458353</v>
+        <v>457868</v>
       </c>
       <c r="R16" t="n">
-        <v>6926238</v>
+        <v>6925885</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848585</v>
+        <v>124848562</v>
       </c>
       <c r="B11" t="n">
-        <v>88512</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457899</v>
+        <v>457950</v>
       </c>
       <c r="R11" t="n">
-        <v>6925794</v>
+        <v>6925736</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,6 +1684,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848562</v>
+        <v>124848585</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
+        <v>88512</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457950</v>
+        <v>457899</v>
       </c>
       <c r="R12" t="n">
-        <v>6925736</v>
+        <v>6925794</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,11 +1791,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>124848564</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>124848561</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>124848566</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>124848562</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>124848567</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>124848564</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>124848561</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>124848566</v>
       </c>
       <c r="B8" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>124848562</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>124848567</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 12431-2025 artfynd.xlsx
+++ b/artfynd/A 12431-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>124848564</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>124848561</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>124848566</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>124848562</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>124848567</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
